--- a/Test Results/Excel/Summary_Report.xlsx
+++ b/Test Results/Excel/Summary_Report.xlsx
@@ -4,14 +4,15 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Summary Report" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Executive Summary" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Module Breakdown" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="35">
   <si>
     <t>Metric</t>
   </si>
@@ -19,41 +20,110 @@
     <t>Value</t>
   </si>
   <si>
-    <t>Target Environment</t>
-  </si>
-  <si>
-    <t>LIVE GitHub Pages (HTTPS)</t>
-  </si>
-  <si>
-    <t>BASE_URL</t>
-  </si>
-  <si>
-    <t>https://Anjali-0710.github.io/FoodShare/</t>
-  </si>
-  <si>
-    <t>Total Executed Tests</t>
-  </si>
-  <si>
-    <t>Passed Tests</t>
-  </si>
-  <si>
-    <t>Failed Tests</t>
-  </si>
-  <si>
-    <t>Skipped Tests</t>
+    <t>📊 Total Test Cases</t>
+  </si>
+  <si>
+    <t>✅ Passed</t>
+  </si>
+  <si>
+    <t>❌ Failed</t>
+  </si>
+  <si>
+    <t>⏭️ Skipped</t>
+  </si>
+  <si>
+    <t>🎯 Pass Rate</t>
+  </si>
+  <si>
+    <t>100.00%</t>
+  </si>
+  <si>
+    <t>📅 Execution Date</t>
+  </si>
+  <si>
+    <t>20/8/2026, 1:22:07 pm</t>
+  </si>
+  <si>
+    <t>🌐 Target Application</t>
+  </si>
+  <si>
+    <t>https://nagaanjali0710.github.io/FOODREACH_PDD/</t>
+  </si>
+  <si>
+    <t>🔧 Framework</t>
+  </si>
+  <si>
+    <t>Selenium WebDriver 4.x + Mocha 10.x</t>
+  </si>
+  <si>
+    <t>🖥️ Browser</t>
+  </si>
+  <si>
+    <t>Google Chrome Headless</t>
+  </si>
+  <si>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>Skipped</t>
   </si>
   <si>
     <t>Pass Rate</t>
   </si>
   <si>
-    <t>100.00%</t>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>login</t>
+  </si>
+  <si>
+    <t>100.0%</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>register</t>
+  </si>
+  <si>
+    <t>donor</t>
+  </si>
+  <si>
+    <t>ngo</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>volunteer</t>
+  </si>
+  <si>
+    <t>notifications</t>
+  </si>
+  <si>
+    <t>profile</t>
+  </si>
+  <si>
+    <t>maps</t>
+  </si>
+  <si>
+    <t>security</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -63,10 +133,15 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF065F46"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -75,7 +150,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0F172A"/>
+        <fgColor rgb="FF1565C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7C3AED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,9 +176,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -433,13 +524,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="30" customWidth="1"/>
+    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -451,48 +543,48 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
+      <c r="B2">
+        <v>470</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>470</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B4">
-        <v>470</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>470</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
         <v>9</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -501,6 +593,292 @@
       </c>
       <c r="B8" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2">
+        <v>50</v>
+      </c>
+      <c r="C2">
+        <v>50</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3">
+        <v>50</v>
+      </c>
+      <c r="C3">
+        <v>50</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4">
+        <v>60</v>
+      </c>
+      <c r="C4">
+        <v>60</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5">
+        <v>60</v>
+      </c>
+      <c r="C5">
+        <v>60</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6">
+        <v>60</v>
+      </c>
+      <c r="C6">
+        <v>60</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7">
+        <v>50</v>
+      </c>
+      <c r="C7">
+        <v>50</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8">
+        <v>40</v>
+      </c>
+      <c r="C8">
+        <v>40</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>40</v>
+      </c>
+      <c r="C9">
+        <v>40</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10">
+        <v>30</v>
+      </c>
+      <c r="C10">
+        <v>30</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11">
+        <v>30</v>
+      </c>
+      <c r="C11">
+        <v>30</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Test Results/Excel/Summary_Report.xlsx
+++ b/Test Results/Excel/Summary_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
   <si>
     <t>Metric</t>
   </si>
@@ -35,13 +35,13 @@
     <t>🎯 Pass Rate</t>
   </si>
   <si>
-    <t>100.00%</t>
+    <t>0.00%</t>
   </si>
   <si>
     <t>📅 Execution Date</t>
   </si>
   <si>
-    <t>20/8/2026, 1:22:07 pm</t>
+    <t>20/8/2026, 2:00:25 pm</t>
   </si>
   <si>
     <t>🌐 Target Application</t>
@@ -86,37 +86,16 @@
     <t>login</t>
   </si>
   <si>
-    <t>100.0%</t>
-  </si>
-  <si>
-    <t>PASS</t>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>FAIL</t>
   </si>
   <si>
     <t>register</t>
   </si>
   <si>
     <t>donor</t>
-  </si>
-  <si>
-    <t>ngo</t>
-  </si>
-  <si>
-    <t>admin</t>
-  </si>
-  <si>
-    <t>volunteer</t>
-  </si>
-  <si>
-    <t>notifications</t>
-  </si>
-  <si>
-    <t>profile</t>
-  </si>
-  <si>
-    <t>maps</t>
-  </si>
-  <si>
-    <t>security</t>
   </si>
 </sst>
 </file>
@@ -138,7 +117,7 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF065F46"/>
+      <color rgb="FF991B1B"/>
     </font>
   </fonts>
   <fills count="5">
@@ -160,7 +139,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
+        <fgColor rgb="FFFEE2E2"/>
       </patternFill>
     </fill>
   </fills>
@@ -544,7 +523,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>470</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -552,7 +531,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>470</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -560,7 +539,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -619,7 +598,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -656,13 +635,13 @@
         <v>23</v>
       </c>
       <c r="B2">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -679,13 +658,13 @@
         <v>26</v>
       </c>
       <c r="B3">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -702,13 +681,13 @@
         <v>27</v>
       </c>
       <c r="B4">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -717,167 +696,6 @@
         <v>24</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5">
-        <v>60</v>
-      </c>
-      <c r="C5">
-        <v>60</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6">
-        <v>60</v>
-      </c>
-      <c r="C6">
-        <v>60</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7">
-        <v>50</v>
-      </c>
-      <c r="C7">
-        <v>50</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8">
-        <v>40</v>
-      </c>
-      <c r="C8">
-        <v>40</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9">
-        <v>40</v>
-      </c>
-      <c r="C9">
-        <v>40</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10">
-        <v>30</v>
-      </c>
-      <c r="C10">
-        <v>30</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11">
-        <v>30</v>
-      </c>
-      <c r="C11">
-        <v>30</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" s="3" t="s">
         <v>25</v>
       </c>
     </row>
